--- a/nriss-patch-2/ig/StructureDefinition-fr-observation-laboratory-report-results-document.xlsx
+++ b/nriss-patch-2/ig/StructureDefinition-fr-observation-laboratory-report-results-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T09:15:45+00:00</t>
+    <t>2026-10-01T07:42:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -699,7 +699,7 @@
     <t>Observation.extension:validateurResultat.extension:typeCode.value[x]</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-participant-additionnel-resultat-cisis|20260619134043</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-participant-additionnel-resultat-cisis|20260916095456</t>
   </si>
   <si>
     <t>Observation.extension:validateurResultat.extension:typeCode.value[x].id</t>
@@ -1319,7 +1319,7 @@
     <t>Observation.category</t>
   </si>
   <si>
-    <t>Code du chapitre</t>
+    <t>Classification of  type of observation</t>
   </si>
   <si>
     <t>A code that classifies the general type of observation being made.</t>
@@ -1839,7 +1839,7 @@
     <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationInterpretation-cisis|20260619134042</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationInterpretation-cisis|20260916095455</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -17920,7 +17920,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
         <v>421</v>
       </c>
@@ -17939,7 +17939,7 @@
         <v>81</v>
       </c>
       <c r="H129" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I129" t="s" s="2">
         <v>82</v>
